--- a/artfynd/A 14090-2025 artfynd.xlsx
+++ b/artfynd/A 14090-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081533</v>
+        <v>125081497</v>
       </c>
       <c r="B2" t="n">
-        <v>58371</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>A 14089, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571032</v>
+        <v>571054</v>
       </c>
       <c r="R2" t="n">
-        <v>6427864</v>
+        <v>6427965</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081497</v>
+        <v>125081533</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,27 +827,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 14089, Hagaberg, Dalhem, Sm</t>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571054</v>
+        <v>571032</v>
       </c>
       <c r="R3" t="n">
-        <v>6427965</v>
+        <v>6427864</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14090-2025 artfynd.xlsx
+++ b/artfynd/A 14090-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081497</v>
+        <v>125081533</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>58371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14089, Hagaberg, Dalhem, Sm</t>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571054</v>
+        <v>571032</v>
       </c>
       <c r="R2" t="n">
-        <v>6427965</v>
+        <v>6427864</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081533</v>
+        <v>125081497</v>
       </c>
       <c r="B3" t="n">
-        <v>58371</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,24 +825,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>A 14089, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571032</v>
+        <v>571054</v>
       </c>
       <c r="R3" t="n">
-        <v>6427864</v>
+        <v>6427965</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14090-2025 artfynd.xlsx
+++ b/artfynd/A 14090-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081533</v>
+        <v>125081497</v>
       </c>
       <c r="B2" t="n">
-        <v>58371</v>
+        <v>57914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +713,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>A 14089, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571032</v>
+        <v>571054</v>
       </c>
       <c r="R2" t="n">
-        <v>6427864</v>
+        <v>6427965</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081497</v>
+        <v>125081533</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>58485</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,27 +827,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 14089, Hagaberg, Dalhem, Sm</t>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571054</v>
+        <v>571032</v>
       </c>
       <c r="R3" t="n">
-        <v>6427965</v>
+        <v>6427864</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14090-2025 artfynd.xlsx
+++ b/artfynd/A 14090-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081497</v>
+        <v>125081533</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
+        <v>58485</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14089, Hagaberg, Dalhem, Sm</t>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571054</v>
+        <v>571032</v>
       </c>
       <c r="R2" t="n">
-        <v>6427965</v>
+        <v>6427864</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081533</v>
+        <v>125081497</v>
       </c>
       <c r="B3" t="n">
-        <v>58485</v>
+        <v>57914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,24 +825,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>A 14089, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571032</v>
+        <v>571054</v>
       </c>
       <c r="R3" t="n">
-        <v>6427864</v>
+        <v>6427965</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14090-2025 artfynd.xlsx
+++ b/artfynd/A 14090-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081533</v>
+        <v>125081497</v>
       </c>
       <c r="B2" t="n">
-        <v>58485</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>A 14089, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571032</v>
+        <v>571054</v>
       </c>
       <c r="R2" t="n">
-        <v>6427864</v>
+        <v>6427965</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081497</v>
+        <v>125081533</v>
       </c>
       <c r="B3" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,27 +817,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 14089, Hagaberg, Dalhem, Sm</t>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571054</v>
+        <v>571032</v>
       </c>
       <c r="R3" t="n">
-        <v>6427965</v>
+        <v>6427864</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14090-2025 artfynd.xlsx
+++ b/artfynd/A 14090-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125081497</v>
       </c>
       <c r="B2" t="n">
-        <v>57932</v>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125081533</v>
       </c>
       <c r="B3" t="n">
-        <v>58505</v>
+        <v>58815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
